--- a/out/Village_map_of_Tiruvallur_Gummidipoondi_Mangalam_13.336793_80.074529.xlsx
+++ b/out/Village_map_of_Tiruvallur_Gummidipoondi_Mangalam_13.336793_80.074529.xlsx
@@ -794,11 +794,6 @@
           <t>13</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>1, 2, 3, 4, 5, 6A, 6B, 6C, 7A, 7B</t>
-        </is>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -806,11 +801,6 @@
           <t>47</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 2, 20, 21, 22, 23, 3A1A1, 3A1B, 3A2, 3B, 3C, 4, 54, 55, 56, 57, 58, 59, 5A1A1A1A1A, 5A1B, 5A2, 5B, 6, 60, 7A, 7B, 8A, 8B, 9</t>
-        </is>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -818,11 +808,6 @@
           <t>28</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>1A, 1B1, 1B2, 2A1, 2A2, 2B1, 2B2, 3A, 3B, 4A, 4B, 5A, 5B, 5C, 6A, 6B, 6C, 6D, 6E, 6F</t>
-        </is>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -830,11 +815,6 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>1A, 1B, 2A, 2B, 3</t>
-        </is>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -842,11 +822,6 @@
           <t>55</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>1, 2</t>
-        </is>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -854,11 +829,6 @@
           <t>52</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 2, 3A, 3B, 4, 5A, 5B, 6A, 6B, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -866,11 +836,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13A, 13B, 14, 2, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -878,11 +843,6 @@
           <t>40</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>1, 2</t>
-        </is>
-      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -890,11 +850,6 @@
           <t>39</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>1, 2, 3A, 3B, 4</t>
-        </is>
-      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -902,11 +857,6 @@
           <t>19</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>1A1, 1A2, 1B, 1C, 1D, 2A, 2B, 3, 4, 5, 6</t>
-        </is>
-      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -914,11 +864,6 @@
           <t>23</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>1, 10A, 10B, 2, 3, 4, 5, 6A, 6B, 6C, 7, 8A1, 8A2, 8B, 9</t>
-        </is>
-      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -926,11 +871,6 @@
           <t>20</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>1, 2, 3, 4, 5, 6A1A, 6A1B, 6A2, 6B1, 6B2, 7</t>
-        </is>
-      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -938,11 +878,6 @@
           <t>25</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>1, 2A, 2B, 2C, 2D1, 2D2, 3A, 3B, 3C, 3D, 3E, 4A1, 4A2, 4B, 5, 5B, 5C, 6A, 6B, 6C, 7A, 7B, 7C, 7D, 7E, 7F, 7G, 7H1A, 7H1B, 7H1C, 7H2, 7I, 7J1, 7J2, 7K, 7L1, 7L2, 7M, 7N, 7O, 7P, 7Q, 7R, 8A1, 8A2, 8B, 9</t>
-        </is>
-      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -950,11 +885,6 @@
           <t>14</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>1, 2, 3A, 3B, 4, 5A, 5B, 6</t>
-        </is>
-      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -962,11 +892,6 @@
           <t>44</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14, 2, 3A, 3B, 3C, 3D, 3E, 3F, 3G, 3H, 4, 5A, 5B, 5C, 5D, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -974,11 +899,6 @@
           <t>34</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>1, 2, 3, 4A, 4B, 4C, 4D, 4E, 5A, 5B, 6, 7</t>
-        </is>
-      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -986,11 +906,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>1, 2, 3A, 3B</t>
-        </is>
-      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -998,11 +913,6 @@
           <t>18</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>1, 2, 3A, 3B, 4A, 4B, 4C, 5, 6, 7</t>
-        </is>
-      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1010,11 +920,6 @@
           <t>38</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>1, 2A, 2B, 3A, 3B, 3C1, 3C2, 3C3, 4A, 4B, 4C, 5A, 5B</t>
-        </is>
-      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1022,11 +927,6 @@
           <t>32</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>1, 10, 11A, 11B, 11C, 11D, 2, 3, 4A, 4B, 5A1, 5A2, 5A3, 5B, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1034,11 +934,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>10, 11, 12, 13A, 13B, 14, 15, 16, 17, 1A, 1B, 2, 3, 4, 5, 6, 7, 8, 9A, 9B</t>
-        </is>
-      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1046,11 +941,6 @@
           <t>29</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>1, 2, 3A, 3B, 4A, 4B, 5, 6, 7</t>
-        </is>
-      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1058,11 +948,6 @@
           <t>37</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>1, 2A, 2B1, 2B2, 2C, 3, 4</t>
-        </is>
-      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1070,11 +955,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>1, 2A, 2B, 2C, 3, 4, 5</t>
-        </is>
-      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1082,21 +962,11 @@
           <t>9</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>1, 2</t>
-        </is>
-      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>1, 2, 3, 4, 5, 6, 7, 8, 9</t>
         </is>
       </c>
     </row>

--- a/out/Village_map_of_Tiruvallur_Gummidipoondi_Mangalam_13.336793_80.074529.xlsx
+++ b/out/Village_map_of_Tiruvallur_Gummidipoondi_Mangalam_13.336793_80.074529.xlsx
@@ -794,6 +794,11 @@
           <t>13</t>
         </is>
       </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6A, 6B, 6C, 7A, 7B</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -801,6 +806,11 @@
           <t>47</t>
         </is>
       </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 2, 20, 21, 22, 23, 3A1A1, 3A1B, 3A2, 3B, 3C, 4, 54, 55, 56, 57, 58, 59, 5A1A1A1A1A, 5A1B, 5A2, 5B, 6, 60, 7A, 7B, 8A, 8B, 9</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -808,6 +818,11 @@
           <t>28</t>
         </is>
       </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>1A, 1B1, 1B2, 2A1, 2A2, 2B1, 2B2, 3A, 3B, 4A, 4B, 5A, 5B, 5C, 6A, 6B, 6C, 6D, 6E, 6F</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -815,6 +830,11 @@
           <t>15</t>
         </is>
       </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2A, 2B, 3</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -822,6 +842,11 @@
           <t>55</t>
         </is>
       </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -829,6 +854,11 @@
           <t>52</t>
         </is>
       </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 2, 3A, 3B, 4, 5A, 5B, 6A, 6B, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -836,6 +866,11 @@
           <t>5</t>
         </is>
       </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13A, 13B, 14, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -843,6 +878,11 @@
           <t>40</t>
         </is>
       </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -850,6 +890,11 @@
           <t>39</t>
         </is>
       </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>1, 2, 3A, 3B, 4</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -857,6 +902,11 @@
           <t>19</t>
         </is>
       </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>1A1, 1A2, 1B, 1C, 1D, 2A, 2B, 3, 4, 5, 6</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -864,6 +914,11 @@
           <t>23</t>
         </is>
       </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>1, 10A, 10B, 2, 3, 4, 5, 6A, 6B, 6C, 7, 8A1, 8A2, 8B, 9</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -871,6 +926,11 @@
           <t>20</t>
         </is>
       </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6A1A, 6A1B, 6A2, 6B1, 6B2, 7</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -878,6 +938,11 @@
           <t>25</t>
         </is>
       </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 2C, 2D1, 2D2, 3A, 3B, 3C, 3D, 3E, 4A1, 4A2, 4B, 5, 5B, 5C, 6A, 6B, 6C, 7A, 7B, 7C, 7D, 7E, 7F, 7G, 7H1A, 7H1B, 7H1C, 7H2, 7I, 7J1, 7J2, 7K, 7L1, 7L2, 7M, 7N, 7O, 7P, 7Q, 7R, 8A1, 8A2, 8B, 9</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -885,6 +950,11 @@
           <t>14</t>
         </is>
       </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>1, 2, 3A, 3B, 4, 5A, 5B, 6</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -892,6 +962,11 @@
           <t>44</t>
         </is>
       </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 2, 3A, 3B, 3C, 3D, 3E, 3F, 3G, 3H, 4, 5A, 5B, 5C, 5D, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -899,6 +974,11 @@
           <t>34</t>
         </is>
       </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4A, 4B, 4C, 4D, 4E, 5A, 5B, 6, 7</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -906,6 +986,11 @@
           <t>6</t>
         </is>
       </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>1, 2, 3A, 3B</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -913,6 +998,11 @@
           <t>18</t>
         </is>
       </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>1, 2, 3A, 3B, 4A, 4B, 4C, 5, 6, 7</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -920,6 +1010,11 @@
           <t>38</t>
         </is>
       </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 3A, 3B, 3C1, 3C2, 3C3, 4A, 4B, 4C, 5A, 5B</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -927,6 +1022,11 @@
           <t>32</t>
         </is>
       </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>1, 10, 11A, 11B, 11C, 11D, 2, 3, 4A, 4B, 5A1, 5A2, 5A3, 5B, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -934,6 +1034,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13A, 13B, 14, 15, 16, 17, 1A, 1B, 2, 3, 4, 5, 6, 7, 8, 9A, 9B</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -941,6 +1046,11 @@
           <t>29</t>
         </is>
       </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>1, 2, 3A, 3B, 4A, 4B, 5, 6, 7</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -948,6 +1058,11 @@
           <t>37</t>
         </is>
       </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B1, 2B2, 2C, 3, 4</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -955,6 +1070,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 2C, 3, 4, 5</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -962,11 +1082,21 @@
           <t>9</t>
         </is>
       </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
           <t>4</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6, 7, 8, 9</t>
         </is>
       </c>
     </row>

--- a/out/Village_map_of_Tiruvallur_Gummidipoondi_Mangalam_13.336793_80.074529.xlsx
+++ b/out/Village_map_of_Tiruvallur_Gummidipoondi_Mangalam_13.336793_80.074529.xlsx
@@ -974,6 +974,11 @@
           <t>34</t>
         </is>
       </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4A, 4B, 4C, 4D, 4E, 5A, 5B, 6, 7</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -981,6 +986,11 @@
           <t>6</t>
         </is>
       </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>1, 2, 3A, 3B</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -988,6 +998,11 @@
           <t>18</t>
         </is>
       </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>1, 2, 3A, 3B, 4A, 4B, 4C, 5, 6, 7</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -995,6 +1010,11 @@
           <t>38</t>
         </is>
       </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 3A, 3B, 3C1, 3C2, 3C3, 4A, 4B, 4C, 5A, 5B</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1002,6 +1022,11 @@
           <t>32</t>
         </is>
       </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>1, 10, 11A, 11B, 11C, 11D, 2, 3, 4A, 4B, 5A1, 5A2, 5A3, 5B, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1009,6 +1034,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13A, 13B, 14, 15, 16, 17, 1A, 1B, 2, 3, 4, 5, 6, 7, 8, 9A, 9B</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1016,6 +1046,11 @@
           <t>29</t>
         </is>
       </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>1, 2, 3A, 3B, 4A, 4B, 5, 6, 7</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1023,6 +1058,11 @@
           <t>37</t>
         </is>
       </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B1, 2B2, 2C, 3, 4</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1030,6 +1070,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 2C, 3, 4, 5</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1037,11 +1082,21 @@
           <t>9</t>
         </is>
       </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
           <t>4</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6, 7, 8, 9</t>
         </is>
       </c>
     </row>
